--- a/outputs/ozon_serum_cards/ozon_serums_2026-08-06.xlsx
+++ b/outputs/ozon_serum_cards/ozon_serums_2026-08-06.xlsx
@@ -1380,10 +1380,14 @@
       <c r="F5" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="G5" s="4" t="n"/>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>Да</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="I5" s="6" t="n"/>
@@ -1538,10 +1542,14 @@
       <c r="F6" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="G6" s="4" t="n"/>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>Да</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="I6" s="6" t="n"/>
@@ -1697,10 +1705,14 @@
       <c r="F7" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="G7" s="4" t="n"/>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>Да</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="I7" s="6" t="n"/>
@@ -1855,10 +1867,14 @@
       <c r="F8" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="G8" s="4" t="n"/>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>Да</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="I8" s="6" t="n"/>
@@ -2013,10 +2029,14 @@
       <c r="F9" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="G9" s="4" t="n"/>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>Да</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="I9" s="6" t="n"/>
@@ -2163,10 +2183,14 @@
       <c r="F10" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="G10" s="4" t="n"/>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>Да</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="I10" s="6" t="n"/>
@@ -2313,10 +2337,14 @@
       <c r="F11" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="G11" s="4" t="n"/>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>Да</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="I11" s="6" t="n"/>
@@ -2472,10 +2500,14 @@
       <c r="F12" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="G12" s="4" t="n"/>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>Да</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="I12" s="6" t="n"/>
@@ -2630,10 +2662,14 @@
       <c r="F13" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="G13" s="4" t="n"/>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>Да</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="I13" s="6" t="n"/>
@@ -2784,10 +2820,14 @@
       <c r="F14" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="G14" s="4" t="n"/>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>Да</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="I14" s="6" t="n"/>
@@ -2939,10 +2979,14 @@
       <c r="F15" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="G15" s="4" t="n"/>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>Да</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="I15" s="6" t="n"/>
@@ -3093,10 +3137,14 @@
       <c r="F16" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="G16" s="4" t="n"/>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>Да</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="I16" s="6" t="n"/>
@@ -3247,10 +3295,14 @@
       <c r="F17" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="G17" s="4" t="n"/>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>Да</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="I17" s="6" t="n"/>
@@ -3407,10 +3459,14 @@
       <c r="F18" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="G18" s="4" t="n"/>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>Да</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="I18" s="6" t="n"/>
@@ -3559,10 +3615,14 @@
       <c r="F19" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="G19" s="4" t="n"/>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>Да</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="I19" s="6" t="n"/>

--- a/outputs/ozon_serum_cards/ozon_serums_2026-08-06.xlsx
+++ b/outputs/ozon_serum_cards/ozon_serums_2026-08-06.xlsx
@@ -1461,7 +1461,7 @@
         </is>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>1080</v>
+        <v>1095</v>
       </c>
       <c r="AB5" s="4" t="n"/>
       <c r="AC5" s="4" t="n"/>
@@ -1623,7 +1623,7 @@
         </is>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>1080</v>
+        <v>1095</v>
       </c>
       <c r="AB6" s="4" t="n"/>
       <c r="AC6" s="4" t="n"/>
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>1080</v>
+        <v>1095</v>
       </c>
       <c r="AB7" s="4" t="n"/>
       <c r="AC7" s="4" t="n"/>
@@ -1948,7 +1948,7 @@
         </is>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>1080</v>
+        <v>1095</v>
       </c>
       <c r="AB8" s="4" t="n"/>
       <c r="AC8" s="4" t="n"/>
@@ -2106,7 +2106,7 @@
         </is>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>1080</v>
+        <v>1095</v>
       </c>
       <c r="AB9" s="4" t="n"/>
       <c r="AC9" s="4" t="n"/>
@@ -2260,7 +2260,7 @@
         </is>
       </c>
       <c r="AA10" s="4" t="n">
-        <v>1080</v>
+        <v>1095</v>
       </c>
       <c r="AB10" s="4" t="n"/>
       <c r="AC10" s="4" t="n"/>
@@ -2418,7 +2418,7 @@
         </is>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>360</v>
+        <v>1095</v>
       </c>
       <c r="AB11" s="4" t="n"/>
       <c r="AC11" s="4" t="n"/>
@@ -2581,7 +2581,7 @@
         </is>
       </c>
       <c r="AA12" s="4" t="n">
-        <v>1080</v>
+        <v>1095</v>
       </c>
       <c r="AB12" s="4" t="n"/>
       <c r="AC12" s="4" t="n"/>
@@ -2743,7 +2743,7 @@
         </is>
       </c>
       <c r="AA13" s="4" t="n">
-        <v>1080</v>
+        <v>1095</v>
       </c>
       <c r="AB13" s="4" t="n"/>
       <c r="AC13" s="4" t="n"/>
@@ -2901,7 +2901,7 @@
         </is>
       </c>
       <c r="AA14" s="4" t="n">
-        <v>1080</v>
+        <v>1095</v>
       </c>
       <c r="AB14" s="4" t="n"/>
       <c r="AC14" s="4" t="n"/>
@@ -3060,7 +3060,7 @@
         </is>
       </c>
       <c r="AA15" s="4" t="n">
-        <v>1080</v>
+        <v>1095</v>
       </c>
       <c r="AB15" s="4" t="n"/>
       <c r="AC15" s="4" t="n"/>
@@ -3218,7 +3218,7 @@
         </is>
       </c>
       <c r="AA16" s="4" t="n">
-        <v>1080</v>
+        <v>1095</v>
       </c>
       <c r="AB16" s="4" t="n"/>
       <c r="AC16" s="4" t="n"/>
@@ -3372,7 +3372,7 @@
         </is>
       </c>
       <c r="AA17" s="4" t="n">
-        <v>1080</v>
+        <v>1095</v>
       </c>
       <c r="AB17" s="4" t="n"/>
       <c r="AC17" s="4" t="n"/>
@@ -3536,7 +3536,7 @@
         </is>
       </c>
       <c r="AA18" s="4" t="n">
-        <v>1080</v>
+        <v>1095</v>
       </c>
       <c r="AB18" s="4" t="n"/>
       <c r="AC18" s="4" t="n"/>
@@ -3696,7 +3696,7 @@
         </is>
       </c>
       <c r="AA19" s="4" t="n">
-        <v>1080</v>
+        <v>1095</v>
       </c>
       <c r="AB19" s="4" t="n"/>
       <c r="AC19" s="4" t="n"/>

--- a/outputs/ozon_serum_cards/ozon_serums_2026-08-06.xlsx
+++ b/outputs/ozon_serum_cards/ozon_serums_2026-08-06.xlsx
@@ -1467,7 +1467,7 @@
       <c r="AC5" s="4" t="n"/>
       <c r="AD5" s="4" t="inlineStr">
         <is>
-          <t>farmstay</t>
+          <t>Myungin Cosmetics Co., Ltd.</t>
         </is>
       </c>
       <c r="AE5" s="4" t="n"/>
@@ -1485,7 +1485,11 @@
       <c r="AI5" s="4" t="n"/>
       <c r="AJ5" s="4" t="n"/>
       <c r="AK5" s="4" t="n"/>
-      <c r="AL5" s="4" t="n"/>
+      <c r="AL5" s="4" t="inlineStr">
+        <is>
+          <t>Нанесите ампулу на очищенную и тонизированную кожу лица (при желании — шеи и зоны декольте) утром и/или вечером. Распределите по коже лёгкими массирующими движениями до впитывания, затем закройте уход кремом.</t>
+        </is>
+      </c>
       <c r="AM5" s="4" t="inlineStr">
         <is>
           <t>Коллаген;Гиалуроновая кислота;Ниацинамид;Витамин С</t>
@@ -1518,7 +1522,9 @@
           <t>Южная Корея</t>
         </is>
       </c>
-      <c r="AU5" s="4" t="n"/>
+      <c r="AU5" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="AV5" s="4" t="n"/>
       <c r="AW5" s="4" t="n"/>
       <c r="AX5" s="4" t="n"/>
@@ -1629,7 +1635,7 @@
       <c r="AC6" s="4" t="n"/>
       <c r="AD6" s="4" t="inlineStr">
         <is>
-          <t>manyo</t>
+          <t>Cosmax Co., Ltd.</t>
         </is>
       </c>
       <c r="AE6" s="4" t="n"/>
@@ -1648,7 +1654,11 @@
       <c r="AI6" s="4" t="n"/>
       <c r="AJ6" s="4" t="n"/>
       <c r="AK6" s="4" t="n"/>
-      <c r="AL6" s="4" t="n"/>
+      <c r="AL6" s="4" t="inlineStr">
+        <is>
+          <t>После очищения и тонизирования нанесите небольшое количество ампулы на лицо и распределите по коже, мягко вбивая подушечками пальцев до полного впитывания. Используйте утром и вечером, затем нанесите крем. При чувствительной коже можно наносить точечно на проблемные зоны.</t>
+        </is>
+      </c>
       <c r="AM6" s="4" t="inlineStr">
         <is>
           <t>Лизат молочнокислых бактерий;Пептиды;Ниацинамид;Пребиотики;Гиалуроновая кислота</t>
@@ -1681,7 +1691,9 @@
           <t>Южная Корея</t>
         </is>
       </c>
-      <c r="AU6" s="4" t="n"/>
+      <c r="AU6" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="AV6" s="4" t="n"/>
       <c r="AW6" s="4" t="n"/>
       <c r="AX6" s="4" t="n"/>
@@ -1792,7 +1804,7 @@
       <c r="AC7" s="4" t="n"/>
       <c r="AD7" s="4" t="inlineStr">
         <is>
-          <t>manyo</t>
+          <t>Manyo Co., Ltd.</t>
         </is>
       </c>
       <c r="AE7" s="4" t="n"/>
@@ -1810,7 +1822,11 @@
       <c r="AI7" s="4" t="n"/>
       <c r="AJ7" s="4" t="n"/>
       <c r="AK7" s="4" t="n"/>
-      <c r="AL7" s="4" t="n"/>
+      <c r="AL7" s="4" t="inlineStr">
+        <is>
+          <t>После умывания и тоника нанесите эссенцию на лицо ладонями, мягко вбивая и распределяя до полного впитывания; можно также нанести на ватный диск и протереть лицо. Применяйте утром и вечером перед кремом. Если параллельно используете средства с витамином C, разнесите их по времени или сделайте паузу около 30 минут.</t>
+        </is>
+      </c>
       <c r="AM7" s="4" t="inlineStr">
         <is>
           <t>Витамин С;Галактомисис;Ниацинамид;Глицерин</t>
@@ -1843,7 +1859,9 @@
           <t>Южная Корея</t>
         </is>
       </c>
-      <c r="AU7" s="4" t="n"/>
+      <c r="AU7" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="AV7" s="4" t="n"/>
       <c r="AW7" s="4" t="n"/>
       <c r="AX7" s="4" t="n"/>
@@ -1954,7 +1972,7 @@
       <c r="AC8" s="4" t="n"/>
       <c r="AD8" s="4" t="inlineStr">
         <is>
-          <t>Elizavecca</t>
+          <t>Miz Trade Inc.</t>
         </is>
       </c>
       <c r="AE8" s="4" t="n"/>
@@ -1972,7 +1990,11 @@
       <c r="AI8" s="4" t="n"/>
       <c r="AJ8" s="4" t="n"/>
       <c r="AK8" s="4" t="n"/>
-      <c r="AL8" s="4" t="n"/>
+      <c r="AL8" s="4" t="inlineStr">
+        <is>
+          <t>Нанесите несколько капель сыворотки на очищенную кожу лица и шеи и распределите лёгкими похлопывающими движениями до впитывания. Можно использовать как маску (пропитать ватные диски и приложить к сухим участкам) или добавить несколько капель в привычный крем. Наносится до более плотных кремов.</t>
+        </is>
+      </c>
       <c r="AM8" s="4" t="inlineStr">
         <is>
           <t>Галактомисис</t>
@@ -2005,7 +2027,9 @@
           <t>Южная Корея</t>
         </is>
       </c>
-      <c r="AU8" s="4" t="n"/>
+      <c r="AU8" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="AV8" s="4" t="n"/>
       <c r="AW8" s="4" t="n"/>
       <c r="AX8" s="4" t="n"/>
@@ -2094,7 +2118,11 @@
       <c r="W9" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="X9" s="4" t="n"/>
+      <c r="X9" s="4" t="inlineStr">
+        <is>
+          <t>Water; Glycereth-26; Glycerin; Dimethicone; Dipropylene Glycol; Niacinamide; Pentaerythrityl Tetraisostearate; Sea Water; Trehalose; Cyclopentasiloxane; Ammonium Acryloyldimethyltaurate/VP Copolymer; Squalane; Sodium Hyaluronate; Hydrolyzed Collagen; Vegetable Amino Acids; Oat Amino Acids; Butylene Glycol; Dimethicone/Vinyl Dimethicone Crosspolymer; Dimethiconol; Hydroxyethyl Acrylate/Sodium Acryloyldimethyl Taurate Copolymer; Polysorbate 60; Carbomer; Arginine; Ethylhexylglycerin; 1,2-Hexanediol; Hydroxyacetophenone; Adenosine; Disodium EDTA; Fragrance (Parfum); Hexyl Cinnamal; Citronellol; Geraniol; Alpha-Isomethyl Ionone; Linalool; Limonene</t>
+        </is>
+      </c>
       <c r="Y9" s="4" t="inlineStr">
         <is>
           <t>Область вокруг глаз</t>
@@ -2112,7 +2140,7 @@
       <c r="AC9" s="4" t="n"/>
       <c r="AD9" s="4" t="inlineStr">
         <is>
-          <t>farmstay</t>
+          <t>Myungin Cosmetics Co., Ltd.</t>
         </is>
       </c>
       <c r="AE9" s="4" t="n"/>
@@ -2126,7 +2154,11 @@
       <c r="AI9" s="4" t="n"/>
       <c r="AJ9" s="4" t="n"/>
       <c r="AK9" s="4" t="n"/>
-      <c r="AL9" s="4" t="n"/>
+      <c r="AL9" s="4" t="inlineStr">
+        <is>
+          <t>На завершающем этапе ухода прокатайте металлическим роликом-аппликатором по коже вокруг глаз, слегка нажимая, чтобы нанести сыворотку тонким слоем. Двигайтесь от внутреннего уголка глаза к внешнему; излишки вбейте подушечками пальцев до полного впитывания. Прохладный ролик помогает снять отёчность.</t>
+        </is>
+      </c>
       <c r="AM9" s="4" t="inlineStr">
         <is>
           <t>Коллаген;Гиалуроновая кислота</t>
@@ -2159,7 +2191,9 @@
           <t>Южная Корея</t>
         </is>
       </c>
-      <c r="AU9" s="4" t="n"/>
+      <c r="AU9" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="AV9" s="4" t="n"/>
       <c r="AW9" s="4" t="n"/>
       <c r="AX9" s="4" t="n"/>
@@ -2248,7 +2282,11 @@
       <c r="W10" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="X10" s="4" t="n"/>
+      <c r="X10" s="4" t="inlineStr">
+        <is>
+          <t>Water; Glycerin; Butylene Glycol; Centella Asiatica Extract; 1,2-Hexanediol; Cellulose Gum; Ethylhexylglycerin</t>
+        </is>
+      </c>
       <c r="Y10" s="4" t="inlineStr">
         <is>
           <t>Лицо</t>
@@ -2266,7 +2304,7 @@
       <c r="AC10" s="4" t="n"/>
       <c r="AD10" s="4" t="inlineStr">
         <is>
-          <t>SKIN1004</t>
+          <t>Craver Corporation</t>
         </is>
       </c>
       <c r="AE10" s="4" t="n"/>
@@ -2280,7 +2318,11 @@
       <c r="AI10" s="4" t="n"/>
       <c r="AJ10" s="4" t="n"/>
       <c r="AK10" s="4" t="n"/>
-      <c r="AL10" s="4" t="n"/>
+      <c r="AL10" s="4" t="inlineStr">
+        <is>
+          <t>Нанесите 2–3 капли ампулы на очищенную кожу после тонера и мягко вбейте подушечками пальцев до впитывания. Используйте утром и вечером перед кремом; на сухие участки можно нанести повторно. Завершите уход увлажняющим кремом, а днём солнцезащитным средством.</t>
+        </is>
+      </c>
       <c r="AM10" s="4" t="inlineStr">
         <is>
           <t>Центелла</t>
@@ -2313,7 +2355,9 @@
           <t>Южная Корея</t>
         </is>
       </c>
-      <c r="AU10" s="4" t="n"/>
+      <c r="AU10" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="AV10" s="4" t="n"/>
       <c r="AW10" s="4" t="n"/>
       <c r="AX10" s="4" t="n"/>
@@ -2424,7 +2468,7 @@
       <c r="AC11" s="4" t="n"/>
       <c r="AD11" s="4" t="inlineStr">
         <is>
-          <t>The ordinary</t>
+          <t>DECIEM Inc.</t>
         </is>
       </c>
       <c r="AE11" s="4" t="n"/>
@@ -2443,7 +2487,11 @@
       <c r="AI11" s="4" t="n"/>
       <c r="AJ11" s="4" t="n"/>
       <c r="AK11" s="4" t="n"/>
-      <c r="AL11" s="4" t="n"/>
+      <c r="AL11" s="4" t="inlineStr">
+        <is>
+          <t>Нанесите несколько капель сыворотки на очищенную кожу всего лица или на проблемные зоны утром и вечером, вбивая ладонями в кожу. Используйте на этапе ухода после очищения и до нанесения крема. Не сочетайте в одном уходе с прямыми кислотами или чистым витамином C.</t>
+        </is>
+      </c>
       <c r="AM11" s="4" t="inlineStr">
         <is>
           <t>Пептиды</t>
@@ -2476,7 +2524,9 @@
           <t>Канада</t>
         </is>
       </c>
-      <c r="AU11" s="4" t="n"/>
+      <c r="AU11" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="AV11" s="4" t="n"/>
       <c r="AW11" s="4" t="n"/>
       <c r="AX11" s="4" t="n"/>
@@ -2587,7 +2637,7 @@
       <c r="AC12" s="4" t="n"/>
       <c r="AD12" s="4" t="inlineStr">
         <is>
-          <t>farmstay</t>
+          <t>Myungin Cosmetics Co., Ltd.</t>
         </is>
       </c>
       <c r="AE12" s="4" t="n"/>
@@ -2605,7 +2655,11 @@
       <c r="AI12" s="4" t="n"/>
       <c r="AJ12" s="4" t="n"/>
       <c r="AK12" s="4" t="n"/>
-      <c r="AL12" s="4" t="n"/>
+      <c r="AL12" s="4" t="inlineStr">
+        <is>
+          <t>Используйте дважды в день после умывания и тоника. Нанесите нужное количество ампулы с муцином улитки на кожу лица и шеи кончиками пальцев и равномерно распределите до впитывания. Средство с лёгкой гелевой текстурой быстро впитывается и не оставляет липкости.</t>
+        </is>
+      </c>
       <c r="AM12" s="4" t="inlineStr">
         <is>
           <t>Муцин улитки;Ниацинамид;Гиалуроновая кислота;Пептиды;Галактомисис</t>
@@ -2638,7 +2692,9 @@
           <t>Южная Корея</t>
         </is>
       </c>
-      <c r="AU12" s="4" t="n"/>
+      <c r="AU12" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="AV12" s="4" t="n"/>
       <c r="AW12" s="4" t="n"/>
       <c r="AX12" s="4" t="n"/>
@@ -2749,7 +2805,7 @@
       <c r="AC13" s="4" t="n"/>
       <c r="AD13" s="4" t="inlineStr">
         <is>
-          <t>round lab</t>
+          <t>COSMOCOS Co., Ltd.</t>
         </is>
       </c>
       <c r="AE13" s="4" t="n"/>
@@ -2763,7 +2819,11 @@
       <c r="AI13" s="4" t="n"/>
       <c r="AJ13" s="4" t="n"/>
       <c r="AK13" s="4" t="n"/>
-      <c r="AL13" s="4" t="n"/>
+      <c r="AL13" s="4" t="inlineStr">
+        <is>
+          <t>Применяйте на этапе эссенции/сыворотки, после тоника, утром и/или вечером. Нанесите 1–2 капли на чистую кожу и мягко вбейте подушечками пальцев по всему лицу до полного впитывания, затем нанесите крем.</t>
+        </is>
+      </c>
       <c r="AM13" s="4" t="inlineStr">
         <is>
           <t>Центелла;LHA-кислота;Гиалуроновая кислота</t>
@@ -2796,7 +2856,9 @@
           <t>Южная Корея</t>
         </is>
       </c>
-      <c r="AU13" s="4" t="n"/>
+      <c r="AU13" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="AV13" s="4" t="n"/>
       <c r="AW13" s="4" t="n"/>
       <c r="AX13" s="4" t="n"/>
@@ -2907,7 +2969,7 @@
       <c r="AC14" s="4" t="n"/>
       <c r="AD14" s="4" t="inlineStr">
         <is>
-          <t>Celimax</t>
+          <t>Absolvlab Inc.</t>
         </is>
       </c>
       <c r="AE14" s="4" t="n"/>
@@ -2922,7 +2984,11 @@
       <c r="AI14" s="4" t="n"/>
       <c r="AJ14" s="4" t="n"/>
       <c r="AK14" s="4" t="n"/>
-      <c r="AL14" s="4" t="n"/>
+      <c r="AL14" s="4" t="inlineStr">
+        <is>
+          <t>Используйте в вечернем уходе после очищения и тонизирования. Нанесите умеренное количество сыворотки на сухую кожу и мягко вбейте подушечками пальцев до впитывания, затем закрепите увлажняющим кремом. В начале применяйте через день, постепенно доводя до ежедневного использования; утром обязательно наносите солнцезащитный крем.</t>
+        </is>
+      </c>
       <c r="AM14" s="4" t="inlineStr">
         <is>
           <t>Ретинол;Микроиглы;Пептиды;Глицерин</t>
@@ -2955,7 +3021,9 @@
           <t>Южная Корея</t>
         </is>
       </c>
-      <c r="AU14" s="4" t="n"/>
+      <c r="AU14" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="AV14" s="4" t="n"/>
       <c r="AW14" s="4" t="n"/>
       <c r="AX14" s="4" t="n"/>
@@ -3066,7 +3134,7 @@
       <c r="AC15" s="4" t="n"/>
       <c r="AD15" s="4" t="inlineStr">
         <is>
-          <t>Celimax</t>
+          <t>Absolvlab Inc.</t>
         </is>
       </c>
       <c r="AE15" s="4" t="n"/>
@@ -3080,7 +3148,11 @@
       <c r="AI15" s="4" t="n"/>
       <c r="AJ15" s="4" t="n"/>
       <c r="AK15" s="4" t="n"/>
-      <c r="AL15" s="4" t="n"/>
+      <c r="AL15" s="4" t="inlineStr">
+        <is>
+          <t>Применяйте утром и вечером после тоника/эссенции и перед кремом. Нанесите 1–2 нажатия ампулы равномерно по лицу подушечками пальцев, избегая области вокруг глаз, и мягко вбейте до полного впитывания. Лучше наносить на слегка влажную кожу для усиления увлажнения.</t>
+        </is>
+      </c>
       <c r="AM15" s="4" t="inlineStr">
         <is>
           <t>Растительный экстракт;Ниацинамид;Коллаген;Пептиды;Глицерин</t>
@@ -3113,7 +3185,9 @@
           <t>Южная Корея</t>
         </is>
       </c>
-      <c r="AU15" s="4" t="n"/>
+      <c r="AU15" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="AV15" s="4" t="n"/>
       <c r="AW15" s="4" t="n"/>
       <c r="AX15" s="4" t="n"/>
@@ -3224,7 +3298,7 @@
       <c r="AC16" s="4" t="n"/>
       <c r="AD16" s="4" t="inlineStr">
         <is>
-          <t>Celimax</t>
+          <t>Absolvlab Inc.</t>
         </is>
       </c>
       <c r="AE16" s="4" t="n"/>
@@ -3238,7 +3312,11 @@
       <c r="AI16" s="4" t="n"/>
       <c r="AJ16" s="4" t="n"/>
       <c r="AK16" s="4" t="n"/>
-      <c r="AL16" s="4" t="n"/>
+      <c r="AL16" s="4" t="inlineStr">
+        <is>
+          <t>Используйте утром и вечером после очищения и тонизирования, перед кремом. Нанесите умеренное количество равномерно по лицу, уделяя внимание участкам с пигментацией и расширенными порами, и мягко вбейте до впитывания. Днём завершайте уход солнцезащитным кремом.</t>
+        </is>
+      </c>
       <c r="AM16" s="4" t="inlineStr">
         <is>
           <t>Ниацинамид;Глицерин</t>
@@ -3271,7 +3349,9 @@
           <t>Южная Корея</t>
         </is>
       </c>
-      <c r="AU16" s="4" t="n"/>
+      <c r="AU16" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="AV16" s="4" t="n"/>
       <c r="AW16" s="4" t="n"/>
       <c r="AX16" s="4" t="n"/>
@@ -3360,7 +3440,11 @@
       <c r="W17" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="X17" s="4" t="n"/>
+      <c r="X17" s="4" t="inlineStr">
+        <is>
+          <t>Bifida Ferment Lysate; Methylpropanediol; Dipropylene Glycol; Butylene Glycol; 1,2-Hexanediol; Niacinamide; Water; Glycerin; Pentylene Glycol; Chlorella Vulgaris Extract; Hydrolyzed Sponge; Theobroma Cacao (Cocoa) Extract; Sodium Hyaluronate; Glyceryl Polymethacrylate; Polyglyceryl-10 Laurate; Ammonium Acryloyldimethyltaurate/VP Copolymer; Glucose; Acrylates/C10-30 Alkyl Acrylate Crosspolymer; Diethoxyethyl Succinate; Hydrogenated Lecithin; Fructooligosaccharides; Fructose; Hydrogenated Polyisobutene; Panthenol; Tromethamine; Ethylhexylglycerin; Allantoin; Adenosine; Dextrin; Gluconolactone; Sodium Phytate; Caprylic/Capric Triglyceride; Tocopherol; Ceramide NP; Hyaluronic Acid/Polyisopropylacrylamide Copolymer; Sodium Stearoyl Glutamate</t>
+        </is>
+      </c>
       <c r="Y17" s="4" t="inlineStr">
         <is>
           <t>Лицо</t>
@@ -3378,7 +3462,7 @@
       <c r="AC17" s="4" t="n"/>
       <c r="AD17" s="4" t="inlineStr">
         <is>
-          <t>manyo</t>
+          <t>Manyo Co., Ltd.</t>
         </is>
       </c>
       <c r="AE17" s="4" t="n"/>
@@ -3402,7 +3486,11 @@
       <c r="AI17" s="4" t="n"/>
       <c r="AJ17" s="4" t="n"/>
       <c r="AK17" s="4" t="n"/>
-      <c r="AL17" s="4" t="n"/>
+      <c r="AL17" s="4" t="inlineStr">
+        <is>
+          <t>Хорошо встряхните флакон перед применением. После очищения и тоника нанесите ампулу на лицо и мягко вбейте подушечками пальцев до впитывания — вы можете почувствовать лёгкое покалывание от микроспикул, это нормально. Используйте вечером 2–3 раза в неделю, начиная с малого количества, затем нанесите увлажняющий крем; в дни применения обязательно пользуйтесь SPF днём.</t>
+        </is>
+      </c>
       <c r="AM17" s="4" t="inlineStr">
         <is>
           <t>Лизат молочнокислых бактерий;Микроиглы;Пептиды</t>
@@ -3435,7 +3523,9 @@
           <t>Южная Корея</t>
         </is>
       </c>
-      <c r="AU17" s="4" t="n"/>
+      <c r="AU17" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="AV17" s="4" t="n"/>
       <c r="AW17" s="4" t="n"/>
       <c r="AX17" s="4" t="n"/>
@@ -3524,7 +3614,11 @@
       <c r="W18" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="X18" s="4" t="n"/>
+      <c r="X18" s="4" t="inlineStr">
+        <is>
+          <t>Water; Isopropyl Myristate; Panax Ginseng Root Extract; Caprylic/Capric Triglyceride; Cetyl Ethylhexanoate; Glycerin; Propanediol; Niacinamide; Polyglyceryl-2 Dipolyhydroxystearate; PEG-30 Dipolyhydroxystearate; Polyglyceryl-3 Diisostearate; 1,2-Hexanediol; Tocopherol; Hydroxyacetophenone; Helianthus Annuus (Sunflower) Seed Oil; Acrylates/C10-30 Alkyl Acrylate Crosspolymer; Arginine; Adenosine; Ceramide NP; Adansonia Digitata Seed Oil; Disodium EDTA; Hydrogenated Lecithin; Allantoin; Squalane; Polyglucuronic Acid; Ceramide NS; Ceramide AS; Ceramide EOP; Ceramide AP; Sodium DNA</t>
+        </is>
+      </c>
       <c r="Y18" s="4" t="inlineStr">
         <is>
           <t>Лицо</t>
@@ -3542,7 +3636,7 @@
       <c r="AC18" s="4" t="n"/>
       <c r="AD18" s="4" t="inlineStr">
         <is>
-          <t>VT COSMETICS</t>
+          <t>Hanacos Co., Ltd.</t>
         </is>
       </c>
       <c r="AE18" s="4" t="n"/>
@@ -3558,7 +3652,11 @@
       <c r="AI18" s="4" t="n"/>
       <c r="AJ18" s="4" t="n"/>
       <c r="AK18" s="4" t="n"/>
-      <c r="AL18" s="4" t="n"/>
+      <c r="AL18" s="4" t="inlineStr">
+        <is>
+          <t>После умывания нанесите небольшое количество эссенции на лицо и распределите от центра к периферии, слегка вдавливая подушечками пальцев до полного впитывания. В вечернем уходе используйте после бустеров с микроиглами, затем завершите уход кремом. Подходит для всех типов кожи.</t>
+        </is>
+      </c>
       <c r="AM18" s="4" t="inlineStr">
         <is>
           <t>PDRN;Ниацинамид</t>
@@ -3591,7 +3689,9 @@
           <t>Южная Корея</t>
         </is>
       </c>
-      <c r="AU18" s="4" t="n"/>
+      <c r="AU18" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="AV18" s="4" t="n"/>
       <c r="AW18" s="4" t="n"/>
       <c r="AX18" s="4" t="n"/>
@@ -3702,7 +3802,7 @@
       <c r="AC19" s="4" t="n"/>
       <c r="AD19" s="4" t="inlineStr">
         <is>
-          <t>VT COSMETICS</t>
+          <t>VT Cosmetics Inc.</t>
         </is>
       </c>
       <c r="AE19" s="4" t="n"/>
@@ -3719,7 +3819,11 @@
       <c r="AI19" s="4" t="n"/>
       <c r="AJ19" s="4" t="n"/>
       <c r="AK19" s="4" t="n"/>
-      <c r="AL19" s="4" t="n"/>
+      <c r="AL19" s="4" t="inlineStr">
+        <is>
+          <t>В вечернем уходе нанесите средство на очищенную кожу, распределите пальцами и дайте полностью впитаться, затем продолжите уход тонером и кремом. В начале применяйте раз в 3 дня, постепенно доводя до ежедневного использования; лёгкое покалывание при первых применениях считается нормой. Днём обязательно используйте солнцезащитный крем SPF50 PA++++.</t>
+        </is>
+      </c>
       <c r="AM19" s="4" t="inlineStr">
         <is>
           <t>Микроиглы;Ниацинамид;Масло;Пептиды</t>
@@ -3752,7 +3856,9 @@
           <t>Южная Корея</t>
         </is>
       </c>
-      <c r="AU19" s="4" t="n"/>
+      <c r="AU19" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="AV19" s="4" t="n"/>
       <c r="AW19" s="4" t="n"/>
       <c r="AX19" s="4" t="n"/>
